--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555637457</v>
+        <v>46157.93113430731</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113430731</v>
+        <v>46157.9313701589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313701589</v>
+        <v>46157.93384420752</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384420752</v>
+        <v>46157.93696199932</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696199932</v>
+        <v>46158.28205158588</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205158588</v>
+        <v>46158.29652885989</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652885989</v>
+        <v>46158.29808037097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808037097</v>
+        <v>46158.33370819818</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370819818</v>
+        <v>46158.37221996904</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июнь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221996904</v>
+        <v>46158.37275831455</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
